--- a/cancellation_forms/044_fitness_training_cancellation_form--cancellation_forms.xlsx
+++ b/cancellation_forms/044_fitness_training_cancellation_form--cancellation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -823,8 +823,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'illness/injury'}</t>
+          <t>illness/injury</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Illness/Injury'}</t>
+          <t>Illness/Injury</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'no_interest'}</t>
+          <t>no_interest</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'No interest'}</t>
+          <t>No interest</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'work/school_commitment'}</t>
+          <t>work/school_commitment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Work/School commitment'}</t>
+          <t>Work/School commitment</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'personal_reasons'}</t>
+          <t>personal_reasons</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Personal reasons'}</t>
+          <t>Personal reasons</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'personalized_coaching'}</t>
+          <t>personalized_coaching</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Personalized coaching'}</t>
+          <t>Personalized coaching</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'nutrition'}</t>
+          <t>nutrition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Nutrition'}</t>
+          <t>Nutrition</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'mindfulness'}</t>
+          <t>mindfulness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Mindfulness'}</t>
+          <t>Mindfulness</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'yoga'}</t>
+          <t>yoga</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Yoga'}</t>
+          <t>Yoga</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'pilates'}</t>
+          <t>pilates</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Pilates'}</t>
+          <t>Pilates</t>
         </is>
       </c>
     </row>
